--- a/results/tables/Tablas_cuerpo.xlsx
+++ b/results/tables/Tablas_cuerpo.xlsx
@@ -789,7 +789,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC95%: intervalo de confianza al 95%. BYM2: modelo espacial bayesiano Besag-York-Mollié tipo 2. HTA: hipertensión arterial. pp: puntos porcentuales.</t>
+          <t>IC95%: intervalo de confianza al 95%. Las estimaciones BYM2 son probabilidades condicionales estandarizadas a la composición adulta censal; las directas usan los denominadores clínicos de la encuesta. BYM2: modelo espacial bayesiano Besag-York-Mollié tipo 2. HTA: hipertensión arterial. pp: puntos porcentuales.</t>
         </is>
       </c>
     </row>
